--- a/data/trans_dic/P29A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P29A_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,32; 46,61</t>
+          <t>40,42; 46,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,44; 52,31</t>
+          <t>45,69; 52,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,34; 48,84</t>
+          <t>41,92; 48,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,16; 51,4</t>
+          <t>43,55; 52,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,81; 13,08</t>
+          <t>9,6; 13,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,53; 16,58</t>
+          <t>12,53; 16,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 15,12</t>
+          <t>10,67; 14,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 11,07</t>
+          <t>7,43; 10,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,5; 27,21</t>
+          <t>23,6; 27,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,69; 30,68</t>
+          <t>26,81; 30,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,51; 28,76</t>
+          <t>24,55; 28,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,54; 26,73</t>
+          <t>22,61; 26,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,54; 62,47</t>
+          <t>57,98; 62,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,9; 59,62</t>
+          <t>54,74; 59,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,33; 60,87</t>
+          <t>56,24; 60,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,6; 49,2</t>
+          <t>31,87; 49,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,12; 33,77</t>
+          <t>29,0; 33,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,93; 31,57</t>
+          <t>26,89; 31,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,48; 36,67</t>
+          <t>32,63; 36,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,1; 51,35</t>
+          <t>24,14; 49,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,47; 47,83</t>
+          <t>44,4; 48,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,28; 45,56</t>
+          <t>42,16; 45,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,22; 48,47</t>
+          <t>45,18; 48,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>32,05; 46,0</t>
+          <t>31,75; 45,57</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,21; 64,56</t>
+          <t>55,87; 64,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,91; 70,14</t>
+          <t>60,44; 70,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,33; 71,72</t>
+          <t>63,22; 71,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,21; 57,68</t>
+          <t>49,35; 57,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,08; 42,72</t>
+          <t>33,36; 42,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,58; 50,79</t>
+          <t>40,35; 50,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,15; 54,07</t>
+          <t>45,43; 54,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,13; 40,64</t>
+          <t>34,23; 40,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47,21; 53,33</t>
+          <t>46,92; 53,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52,06; 59,0</t>
+          <t>52,17; 58,87</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,59; 61,77</t>
+          <t>55,58; 61,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,52; 48,03</t>
+          <t>42,55; 48,2</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>53,24; 56,61</t>
+          <t>52,95; 56,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,17; 57,78</t>
+          <t>54,33; 57,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,53; 58,8</t>
+          <t>55,28; 58,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36,23; 49,71</t>
+          <t>34,8; 49,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,05; 25,95</t>
+          <t>23,1; 26,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,14; 27,2</t>
+          <t>24,16; 27,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,25; 32,35</t>
+          <t>29,14; 32,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,27; 41,53</t>
+          <t>23,26; 43,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,24; 40,67</t>
+          <t>38,25; 40,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,16; 41,71</t>
+          <t>39,2; 41,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42,43; 44,81</t>
+          <t>42,37; 44,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,26; 42,61</t>
+          <t>33,06; 42,7</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>411794; 476041</t>
+          <t>412864; 474694</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>422655; 486482</t>
+          <t>424939; 487081</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>302283; 357103</t>
+          <t>306486; 357766</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>221321; 263542</t>
+          <t>223297; 266681</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>128746; 171547</t>
+          <t>125912; 170506</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>164978; 218234</t>
+          <t>164914; 219251</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>105202; 148709</t>
+          <t>104994; 146699</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56863; 83174</t>
+          <t>55850; 82445</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>548342; 634921</t>
+          <t>550575; 636498</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>599524; 689141</t>
+          <t>602236; 690807</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>420241; 493193</t>
+          <t>421060; 495240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>284887; 337874</t>
+          <t>285781; 339622</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>960025; 1042307</t>
+          <t>967358; 1044398</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1027758; 1116154</t>
+          <t>1024673; 1113933</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1133928; 1225426</t>
+          <t>1132134; 1227833</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>699603; 1124623</t>
+          <t>728636; 1122017</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>458109; 531242</t>
+          <t>456114; 531836</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>463691; 543681</t>
+          <t>462984; 545080</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>637267; 719490</t>
+          <t>640116; 723761</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>538576; 1147301</t>
+          <t>539320; 1113278</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1441522; 1550267</t>
+          <t>1439343; 1556699</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1519529; 1637613</t>
+          <t>1515101; 1639152</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1797507; 1926781</t>
+          <t>1796115; 1928551</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1448818; 2079391</t>
+          <t>1435054; 2059725</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>305051; 350391</t>
+          <t>303205; 351643</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>283543; 326519</t>
+          <t>281387; 327353</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>333390; 377565</t>
+          <t>332804; 376695</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>318231; 372953</t>
+          <t>319084; 370650</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>162024; 203086</t>
+          <t>158605; 201053</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>180089; 225443</t>
+          <t>179106; 225537</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>239315; 286583</t>
+          <t>240781; 287151</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>224711; 267566</t>
+          <t>225320; 269845</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>480685; 542948</t>
+          <t>477649; 545431</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>473411; 536539</t>
+          <t>474439; 535337</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>587274; 652628</t>
+          <t>587183; 650324</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>554796; 626819</t>
+          <t>555227; 629010</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1721081; 1830050</t>
+          <t>1711533; 1832417</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1769988; 1888008</t>
+          <t>1775398; 1892129</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1816376; 1923115</t>
+          <t>1808004; 1921889</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1248334; 1712669</t>
+          <t>1198957; 1717427</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>774438; 871859</t>
+          <t>776264; 875351</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>840574; 947231</t>
+          <t>841136; 950343</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1016756; 1124449</t>
+          <t>1012874; 1122647</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>847834; 1513290</t>
+          <t>847639; 1585459</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2521204; 2681089</t>
+          <t>2521776; 2683702</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2642961; 2815066</t>
+          <t>2646168; 2817569</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2862262; 3023349</t>
+          <t>2858349; 3023574</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2357641; 3020393</t>
+          <t>2343538; 3027093</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P29A_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P29A_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,42; 46,48</t>
+          <t>40,61; 46,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,69; 52,37</t>
+          <t>45,78; 52,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,92; 48,93</t>
+          <t>41,93; 49,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43,55; 52,01</t>
+          <t>40,79; 49,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 13,0</t>
+          <t>9,6; 13,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,53; 16,66</t>
+          <t>12,48; 16,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,67; 14,91</t>
+          <t>10,67; 14,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 10,97</t>
+          <t>7,65; 10,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,6; 27,28</t>
+          <t>23,36; 27,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26,81; 30,75</t>
+          <t>26,67; 30,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,55; 28,88</t>
+          <t>24,61; 28,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,61; 26,87</t>
+          <t>22,08; 26,1</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,98; 62,59</t>
+          <t>57,4; 62,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54,74; 59,51</t>
+          <t>55,12; 59,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56,24; 60,99</t>
+          <t>56,28; 60,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,87; 49,08</t>
+          <t>44,68; 49,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,0; 33,81</t>
+          <t>29,05; 33,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,89; 31,65</t>
+          <t>26,77; 31,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,63; 36,89</t>
+          <t>32,71; 36,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,14; 49,83</t>
+          <t>24,11; 27,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,4; 48,02</t>
+          <t>44,51; 48,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,16; 45,61</t>
+          <t>42,17; 45,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45,18; 48,52</t>
+          <t>45,21; 48,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,75; 45,57</t>
+          <t>35,04; 38,3</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,19%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,87; 64,79</t>
+          <t>55,79; 64,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,44; 70,32</t>
+          <t>60,78; 70,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,22; 71,55</t>
+          <t>62,99; 71,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,35; 57,32</t>
+          <t>47,74; 56,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,36; 42,29</t>
+          <t>34,46; 43,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,35; 50,82</t>
+          <t>40,06; 50,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,43; 54,18</t>
+          <t>45,8; 54,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,23; 40,99</t>
+          <t>33,82; 40,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46,92; 53,57</t>
+          <t>47,1; 53,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52,17; 58,87</t>
+          <t>51,94; 59,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55,58; 61,56</t>
+          <t>55,6; 61,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,55; 48,2</t>
+          <t>41,58; 46,61</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>52,95; 56,69</t>
+          <t>53,22; 56,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,33; 57,91</t>
+          <t>54,37; 57,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,28; 58,76</t>
+          <t>55,42; 58,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,8; 49,85</t>
+          <t>45,7; 49,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,1; 26,05</t>
+          <t>22,97; 25,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,16; 27,29</t>
+          <t>24,34; 27,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,14; 32,3</t>
+          <t>29,29; 32,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,26; 43,51</t>
+          <t>23,08; 25,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,25; 40,71</t>
+          <t>38,1; 40,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,2; 41,74</t>
+          <t>39,21; 41,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42,37; 44,82</t>
+          <t>42,41; 44,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,06; 42,7</t>
+          <t>34,62; 36,94</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>243958</t>
+          <t>258511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>311290</t>
+          <t>333444</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>412864; 474694</t>
+          <t>414737; 475387</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>424939; 487081</t>
+          <t>425762; 486256</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>306486; 357766</t>
+          <t>306552; 360553</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>223297; 266681</t>
+          <t>235067; 282618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>125912; 170506</t>
+          <t>125949; 172206</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>164914; 219251</t>
+          <t>164283; 216216</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>104994; 146699</t>
+          <t>104982; 147167</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>55850; 82445</t>
+          <t>62712; 88715</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>550575; 636498</t>
+          <t>544962; 632514</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>602236; 690807</t>
+          <t>599176; 692799</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>421060; 495240</t>
+          <t>422011; 495385</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>285781; 339622</t>
+          <t>308072; 364234</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>985825</t>
+          <t>1047639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>709850</t>
+          <t>560023</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1695675</t>
+          <t>1607662</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>967358; 1044398</t>
+          <t>957699; 1038337</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1024673; 1113933</t>
+          <t>1031920; 1116684</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1132134; 1227833</t>
+          <t>1132981; 1225005</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>728636; 1122017</t>
+          <t>994589; 1101580</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>456114; 531836</t>
+          <t>456932; 528898</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>462984; 545080</t>
+          <t>460936; 538623</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>640116; 723761</t>
+          <t>641713; 724630</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>539320; 1113278</t>
+          <t>522430; 596926</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1439343; 1556699</t>
+          <t>1442771; 1558692</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1515101; 1639152</t>
+          <t>1515592; 1636647</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1796115; 1928551</t>
+          <t>1797255; 1926287</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1435054; 2059725</t>
+          <t>1539178; 1682491</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>344253</t>
+          <t>368029</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>246303</t>
+          <t>270040</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>590556</t>
+          <t>638069</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>303205; 351643</t>
+          <t>302759; 350263</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>281387; 327353</t>
+          <t>282967; 328376</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>332804; 376695</t>
+          <t>331621; 374905</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>319084; 370650</t>
+          <t>339703; 399170</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>158605; 201053</t>
+          <t>163822; 206206</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>179106; 225537</t>
+          <t>177810; 223335</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>240781; 287151</t>
+          <t>242728; 287260</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>225320; 269845</t>
+          <t>247700; 296070</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>477649; 545431</t>
+          <t>479497; 545320</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>474439; 535337</t>
+          <t>472332; 539329</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>587183; 650324</t>
+          <t>587435; 652261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>555227; 629010</t>
+          <t>600470; 673125</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1574035</t>
+          <t>1674178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1023486</t>
+          <t>904997</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2597521</t>
+          <t>2579176</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1711533; 1832417</t>
+          <t>1720474; 1832180</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1775398; 1892129</t>
+          <t>1776735; 1886734</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1808004; 1921889</t>
+          <t>1812574; 1925510</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1198957; 1717427</t>
+          <t>1605796; 1744327</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>776264; 875351</t>
+          <t>771836; 872284</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>841136; 950343</t>
+          <t>847561; 947203</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1012874; 1122647</t>
+          <t>1017917; 1121170</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>847639; 1585459</t>
+          <t>858469; 954603</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2521776; 2683702</t>
+          <t>2512024; 2675544</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2646168; 2817569</t>
+          <t>2646670; 2813156</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2858349; 3023574</t>
+          <t>2861088; 3019203</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2343538; 3027093</t>
+          <t>2503982; 2671552</t>
         </is>
       </c>
     </row>
